--- a/Assets/Excels/GoldData.xlsx
+++ b/Assets/Excels/GoldData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valha\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B991DDCD-B04D-41C0-B6FE-FF6D1C6F958D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95AA2DD-6F86-4DB5-9B04-F95F55C5097E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A2FBB184-D53B-4402-B88A-FC0966308538}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{A2FBB184-D53B-4402-B88A-FC0966308538}"/>
   </bookViews>
   <sheets>
     <sheet name="GoldData" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,11 +50,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>goldpersec</t>
+    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
+    <t>gaingold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sec</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -469,17 +473,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174C6A6E-5A87-428C-A0F5-E60183A43997}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col min="3" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -490,24 +494,30 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5001</v>
       </c>
@@ -518,10 +528,13 @@
         <v>25</v>
       </c>
       <c r="D3" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5002</v>
       </c>
@@ -532,10 +545,13 @@
         <v>25</v>
       </c>
       <c r="D4" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5003</v>
       </c>
@@ -546,10 +562,13 @@
         <v>25</v>
       </c>
       <c r="D5" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5004</v>
       </c>
@@ -560,10 +579,13 @@
         <v>25</v>
       </c>
       <c r="D6" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5005</v>
       </c>
@@ -574,10 +596,13 @@
         <v>25</v>
       </c>
       <c r="D7" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5006</v>
       </c>
@@ -588,10 +613,13 @@
         <v>25</v>
       </c>
       <c r="D8" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5007</v>
       </c>
@@ -602,10 +630,13 @@
         <v>25</v>
       </c>
       <c r="D9" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5008</v>
       </c>
@@ -616,6 +647,9 @@
         <v>25</v>
       </c>
       <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1">
         <v>10</v>
       </c>
     </row>

--- a/Assets/Excels/GoldData.xlsx
+++ b/Assets/Excels/GoldData.xlsx
@@ -1,131 +1,656 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95AA2DD-6F86-4DB5-9B04-F95F55C5097E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild="10.105.262.54977"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{A2FBB184-D53B-4402-B88A-FC0966308538}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="590" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="GoldData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>stagenum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>startgold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>gaingold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>sec</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="21">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="10"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -136,23 +661,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="3" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
+    <cellStyle name="열어본 하이퍼링크" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="2" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="5" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="6" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -472,18 +1035,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174C6A6E-5A87-428C-A0F5-E60183A43997}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="1" style="1" width="7.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="1" width="9.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="4" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="1" width="10.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -500,7 +1063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -517,9 +1080,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="1">
-        <v>5001</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -534,9 +1097,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="1">
-        <v>5002</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -551,9 +1114,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
-        <v>5003</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -568,9 +1131,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
-        <v>5004</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>4</v>
@@ -585,9 +1148,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
-        <v>5005</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
@@ -602,9 +1165,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <v>5006</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>6</v>
@@ -619,9 +1182,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
-        <v>5007</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>7</v>
@@ -636,9 +1199,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <v>5008</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>8</v>
@@ -655,6 +1218,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/Excels/GoldData.xlsx
+++ b/Assets/Excels/GoldData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E307044-40D7-4F9F-9113-58CEBF35FC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D5834A-078C-4351-8574-438A09865D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5145" yWindow="5370" windowWidth="21600" windowHeight="8955" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GoldData" sheetId="1" r:id="rId1"/>
@@ -529,13 +529,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">

--- a/Assets/Excels/GoldData.xlsx
+++ b/Assets/Excels/GoldData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\새 폴더\T4-GitHub\Assets\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D5834A-078C-4351-8574-438A09865D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5145" yWindow="5370" windowWidth="21600" windowHeight="8955" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5148" yWindow="5376" windowWidth="21600" windowHeight="8952" tabRatio="590"/>
   </bookViews>
   <sheets>
     <sheet name="GoldData" sheetId="1" r:id="rId1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -475,19 +474,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.09765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.8984375" style="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.8984375" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -504,7 +503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -521,7 +520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -529,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="D3" s="1">
         <v>3</v>
@@ -538,7 +537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -555,7 +554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -572,7 +571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -589,7 +588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -606,7 +605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -623,7 +622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -640,7 +639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -660,6 +659,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Excels/GoldData.xlsx
+++ b/Assets/Excels/GoldData.xlsx
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7.09765625" style="1" customWidth="1"/>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="D3" s="1">
         <v>3</v>
@@ -545,13 +545,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>25</v>
+        <v>2000</v>
       </c>
       <c r="D4" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
@@ -562,13 +562,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>25</v>
+        <v>2000</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -579,13 +579,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>25</v>
+        <v>2000</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -596,13 +596,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>25</v>
+        <v>2000</v>
       </c>
       <c r="D7" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -613,47 +613,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="1">
-        <v>25</v>
+        <v>2000</v>
       </c>
       <c r="D8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1">
-        <v>5</v>
-      </c>
-      <c r="E10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/GoldData.xlsx
+++ b/Assets/Excels/GoldData.xlsx
@@ -528,13 +528,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
@@ -545,13 +545,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
@@ -562,13 +562,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -579,13 +579,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -596,13 +596,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -613,13 +613,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="1">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/GoldData.xlsx
+++ b/Assets/Excels/GoldData.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="6" lowestEdited="6" rupBuild="10.105.262.54977"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\T4-GitHub\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="5148" yWindow="5376" windowWidth="21600" windowHeight="8952" tabRatio="590"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="570" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="GoldData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors/>
+  <commentList/>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>id</t>
   </si>
@@ -38,69 +41,361 @@
   <si>
     <t>sec</t>
   </si>
+  <si>
+    <t>SubStagenum</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="22">
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
       <color theme="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <scheme val="minor"/>
+      <color rgb="FF7F7F7F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -115,46 +410,338 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.399980"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="49">
+    <cellStyle name="20% - 강조색1" xfId="25" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="29" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="33" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="37" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="41" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="45" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="26" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="30" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="34" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="38" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="42" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="46" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="27" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="31" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="35" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="39" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="43" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="47" builtinId="52"/>
+    <cellStyle name="강조색1" xfId="24" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="28" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="32" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="36" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="40" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="44" builtinId="49"/>
+    <cellStyle name="경고문" xfId="9" builtinId="11"/>
+    <cellStyle name="계산" xfId="17" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="22" builtinId="27"/>
+    <cellStyle name="메모" xfId="8" builtinId="10"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="보통" xfId="23" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="48" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="18" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표[0]" xfId="6" builtinId="6"/>
+    <cellStyle name="연결된 셀" xfId="19" builtinId="24"/>
     <cellStyle name="열어 본 하이퍼링크" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="20" builtinId="25"/>
+    <cellStyle name="입력" xfId="15" builtinId="20"/>
+    <cellStyle name="제목" xfId="10" builtinId="15"/>
+    <cellStyle name="제목 1" xfId="11" builtinId="16"/>
+    <cellStyle name="제목 2" xfId="12" builtinId="17"/>
+    <cellStyle name="제목 3" xfId="13" builtinId="18"/>
+    <cellStyle name="제목 4" xfId="14" builtinId="19"/>
+    <cellStyle name="좋음" xfId="21" builtinId="26"/>
+    <cellStyle name="출력" xfId="16" builtinId="21"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="7" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8" hidden="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -474,43 +1061,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="7.09765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.8984375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.8984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" style="1" width="7.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="1" width="9.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="5" width="14.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="5" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="1" width="10.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -519,112 +1109,134 @@
       <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
         <v>40</v>
       </c>
-      <c r="D3" s="1">
-        <v>5</v>
-      </c>
       <c r="E3" s="1">
         <v>5</v>
       </c>
+      <c r="F3" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>40</v>
       </c>
-      <c r="D4" s="1">
-        <v>5</v>
-      </c>
       <c r="E4" s="1">
         <v>5</v>
       </c>
+      <c r="F4" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
         <v>3</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>40</v>
       </c>
-      <c r="D5" s="1">
-        <v>5</v>
-      </c>
       <c r="E5" s="1">
         <v>5</v>
       </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1">
         <v>40</v>
       </c>
-      <c r="D6" s="1">
-        <v>5</v>
-      </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
+      <c r="F6" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
         <v>40</v>
       </c>
-      <c r="D7" s="1">
-        <v>5</v>
-      </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D8" s="1">
         <v>40</v>
       </c>
-      <c r="D8" s="1">
-        <v>5</v>
-      </c>
       <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>